--- a/AAII_Financials/Quarterly/TNABY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TNABY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="92">
   <si>
     <t>TNABY</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,62 +656,65 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -739,8 +742,11 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -768,8 +774,11 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -797,8 +806,11 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -810,8 +822,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -839,8 +852,11 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -868,8 +884,11 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -897,8 +916,11 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -926,8 +948,11 @@
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -936,8 +961,9 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -965,8 +991,11 @@
       <c r="K17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -994,8 +1023,11 @@
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1007,8 +1039,9 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1036,8 +1069,11 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1065,8 +1101,11 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1094,8 +1133,11 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1123,8 +1165,11 @@
       <c r="K23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1152,8 +1197,11 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1181,8 +1229,11 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1210,8 +1261,11 @@
       <c r="K26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1239,8 +1293,11 @@
       <c r="K27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1268,8 +1325,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1297,8 +1357,11 @@
       <c r="K29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1326,8 +1389,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1355,8 +1421,11 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1384,8 +1453,11 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1413,8 +1485,11 @@
       <c r="K33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1442,8 +1517,11 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1471,42 +1549,48 @@
       <c r="K35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1518,8 +1602,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1531,269 +1616,297 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3437200</v>
+      </c>
+      <c r="E41" s="3">
         <v>3451400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3094300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3444500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3754800</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="I41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J41" s="3">
         <v>2652600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1984200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>926100</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>957900</v>
+      </c>
+      <c r="E42" s="3">
         <v>782300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>648800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>717400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>748600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3960700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>979900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1264300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2156000</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3926800</v>
+      </c>
+      <c r="E43" s="3">
         <v>4493900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3894300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3798400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3510000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4190700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4463900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5887400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6269000</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>568900</v>
+      </c>
+      <c r="E44" s="3">
         <v>528000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>502400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>557600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>601200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>492800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>409900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>518000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>751300</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>79800</v>
+      </c>
+      <c r="E45" s="3">
         <v>168800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>147600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>142500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>195600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>48800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>89200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>72800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>121800</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9014900</v>
+      </c>
+      <c r="E46" s="3">
         <v>9480800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8336700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8709400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8860600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8692900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8645800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9779800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10286800</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>412300</v>
+      </c>
+      <c r="E47" s="3">
         <v>461400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>437600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>434200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>456400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>472300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>486800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>499900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>486600</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>35038600</v>
+      </c>
+      <c r="E48" s="3">
         <v>37521600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>32913900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>32977900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>34013900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>32624400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>32770100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>34709800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>35155800</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>213000</v>
+      </c>
+      <c r="E49" s="3">
         <v>254300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>249400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>251000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>276900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>301200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>136300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>136900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>135500</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1821,8 +1934,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1850,37 +1966,43 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1095100</v>
+      </c>
+      <c r="E52" s="3">
         <v>1089100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>961200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>937200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>937800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>866200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>871200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>855500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>861400</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1908,37 +2030,43 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>45860500</v>
+      </c>
+      <c r="E54" s="3">
         <v>48904400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>42980600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>43386200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>44630800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>43020000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>42984600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>46059800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>47014200</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1950,8 +2078,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1963,182 +2092,201 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>106700</v>
+      </c>
+      <c r="E57" s="3">
         <v>105900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>100800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>90500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2063900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>92100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>122300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1947800</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2105800</v>
+      </c>
+      <c r="E58" s="3">
         <v>1534900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1308100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1799900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2248300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2152100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2279600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3344300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3744900</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5240100</v>
+      </c>
+      <c r="E59" s="3">
         <v>5750100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4940100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5150300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2159300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4294000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3922500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4139600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2212800</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7596900</v>
+      </c>
+      <c r="E60" s="3">
         <v>7540300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6479500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7171100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7158300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6664400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6451300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7621700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8583900</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>17176100</v>
+      </c>
+      <c r="E61" s="3">
         <v>19079200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>17263600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>17368600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>17946000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>17559600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>17640800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>18646700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>18438400</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>328900</v>
+      </c>
+      <c r="E62" s="3">
         <v>360200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>304900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>301100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>294000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>256000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>244400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>255600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>263500</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2166,8 +2314,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2195,8 +2346,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2224,37 +2378,43 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>31866900</v>
+      </c>
+      <c r="E66" s="3">
         <v>33978200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>29932900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>30661400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>31315700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>30179700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>29996900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>32425200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>33095000</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2266,8 +2426,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2295,8 +2456,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2324,8 +2488,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2353,8 +2520,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2382,37 +2552,43 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>12218800</v>
+      </c>
+      <c r="E72" s="3">
         <v>13021100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>11351200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>11029700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>11555100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>11166400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11272400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>11841200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>12049300</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2440,8 +2616,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2469,8 +2648,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2498,37 +2680,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13501900</v>
+      </c>
+      <c r="E76" s="3">
         <v>14383000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12575500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12266500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12823100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12347400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12493500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13101700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13360100</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2556,42 +2744,48 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2619,8 +2813,11 @@
       <c r="K81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2632,13 +2829,14 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>4</v>
+      <c r="D83" s="3">
+        <v>631600</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>4</v>
@@ -2646,23 +2844,26 @@
       <c r="F83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" s="3">
         <v>2603300</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I83" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L83" s="3">
         <v>2566100</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2690,8 +2891,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2719,8 +2923,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2748,8 +2955,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2777,8 +2987,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2806,37 +3019,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1851200</v>
+      </c>
+      <c r="E89" s="3">
         <v>862500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1259200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>989500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2165800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1267200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2553600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1005700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1223200</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2848,37 +3067,41 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1106300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-479200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-475400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-444400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-945000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-516000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-374300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-474400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-712400</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2906,8 +3129,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2935,37 +3161,43 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1256600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-464500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-379500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-480700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-901300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-505300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-219100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>310300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-653400</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2977,37 +3209,41 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>325000</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>343500</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G96" s="3">
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3">
         <v>227100</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>320500</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3">
         <v>262700</v>
       </c>
     </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3035,8 +3271,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3064,8 +3303,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3093,91 +3335,103 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-368000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-464500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1236600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-710900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-652400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-325200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1566100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-251000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-239300</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-9600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>7200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>2800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>255100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-89400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-355000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-201800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>619000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>427100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>775500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1065600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>330200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TNABY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TNABY_QTR_FIN.xlsx
@@ -1623,7 +1623,7 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3437200</v>
+        <v>3402300</v>
       </c>
       <c r="E41" s="3">
         <v>3451400</v>
@@ -1655,7 +1655,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>957900</v>
+        <v>1015800</v>
       </c>
       <c r="E42" s="3">
         <v>782300</v>
@@ -1687,7 +1687,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3926800</v>
+        <v>3737500</v>
       </c>
       <c r="E43" s="3">
         <v>4493900</v>
@@ -1751,7 +1751,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>79800</v>
+        <v>245900</v>
       </c>
       <c r="E45" s="3">
         <v>168800</v>
@@ -1815,7 +1815,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>412300</v>
+        <v>429300</v>
       </c>
       <c r="E47" s="3">
         <v>461400</v>
@@ -1975,7 +1975,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1095100</v>
+        <v>966600</v>
       </c>
       <c r="E52" s="3">
         <v>1089100</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>106700</v>
+        <v>2207200</v>
       </c>
       <c r="E57" s="3">
         <v>105900</v>
@@ -2163,7 +2163,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5240100</v>
+        <v>2552900</v>
       </c>
       <c r="E59" s="3">
         <v>5750100</v>
@@ -2175,7 +2175,7 @@
         <v>5150300</v>
       </c>
       <c r="H59" s="3">
-        <v>2159300</v>
+        <v>2236400</v>
       </c>
       <c r="I59" s="3">
         <v>4294000</v>
@@ -2227,7 +2227,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>17176100</v>
+        <v>17155100</v>
       </c>
       <c r="E61" s="3">
         <v>19079200</v>
@@ -2259,7 +2259,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>328900</v>
+        <v>349900</v>
       </c>
       <c r="E62" s="3">
         <v>360200</v>
@@ -2836,7 +2836,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>631600</v>
+        <v>2455700</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>4</v>
@@ -3028,7 +3028,7 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1851200</v>
+        <v>1835700</v>
       </c>
       <c r="E89" s="3">
         <v>862500</v>
@@ -3074,7 +3074,7 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1106300</v>
+        <v>-1088400</v>
       </c>
       <c r="E91" s="3">
         <v>-479200</v>
@@ -3170,7 +3170,7 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1256600</v>
+        <v>-1199000</v>
       </c>
       <c r="E94" s="3">
         <v>-464500</v>
@@ -3182,7 +3182,7 @@
         <v>-480700</v>
       </c>
       <c r="H94" s="3">
-        <v>-901300</v>
+        <v>-819600</v>
       </c>
       <c r="I94" s="3">
         <v>-505300</v>
@@ -3344,7 +3344,7 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-368000</v>
+        <v>-445100</v>
       </c>
       <c r="E100" s="3">
         <v>-464500</v>
@@ -3356,7 +3356,7 @@
         <v>-710900</v>
       </c>
       <c r="H100" s="3">
-        <v>-652400</v>
+        <v>-734000</v>
       </c>
       <c r="I100" s="3">
         <v>-325200</v>
@@ -3408,7 +3408,7 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>255100</v>
+        <v>220200</v>
       </c>
       <c r="E102" s="3">
         <v>-89400</v>

--- a/AAII_Financials/Quarterly/TNABY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TNABY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="92">
   <si>
     <t>TNABY</t>
   </si>
@@ -656,65 +656,69 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -745,8 +749,11 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -777,8 +784,11 @@
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -809,8 +819,11 @@
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,8 +836,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -855,8 +869,11 @@
       <c r="L12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -887,8 +904,11 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -919,8 +939,11 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -951,8 +974,11 @@
       <c r="L15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -962,8 +988,9 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -994,8 +1021,11 @@
       <c r="L17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1026,8 +1056,11 @@
       <c r="L18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1040,8 +1073,9 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1072,8 +1106,11 @@
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1104,8 +1141,11 @@
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1136,8 +1176,11 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1168,8 +1211,11 @@
       <c r="L23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1200,8 +1246,11 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1232,8 +1281,11 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1264,8 +1316,11 @@
       <c r="L26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1296,8 +1351,11 @@
       <c r="L27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1328,8 +1386,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1360,8 +1421,11 @@
       <c r="L29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1392,8 +1456,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1424,8 +1491,11 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1456,8 +1526,11 @@
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1488,8 +1561,11 @@
       <c r="L33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1520,8 +1596,11 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1552,45 +1631,51 @@
       <c r="L35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1603,8 +1688,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1617,296 +1703,324 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3779000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3402300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3451400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3094300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3444500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3754800</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="J41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K41" s="3">
         <v>2652600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1984200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>926100</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>916700</v>
+      </c>
+      <c r="E42" s="3">
         <v>1015800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>782300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>648800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>717400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>748600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3960700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>979900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1264300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2156000</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3018800</v>
+      </c>
+      <c r="E43" s="3">
         <v>3737500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4493900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3894300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3798400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3510000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4190700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4463900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5887400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6269000</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>509400</v>
+      </c>
+      <c r="E44" s="3">
         <v>568900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>528000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>502400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>557600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>601200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>492800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>409900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>518000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>751300</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>184900</v>
+      </c>
+      <c r="E45" s="3">
         <v>245900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>168800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>147600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>142500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>195600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>48800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>89200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>72800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>121800</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8454200</v>
+      </c>
+      <c r="E46" s="3">
         <v>9014900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9480800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8336700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8709400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8860600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8692900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8645800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9779800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10286800</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>418300</v>
+      </c>
+      <c r="E47" s="3">
         <v>429300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>461400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>437600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>434200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>456400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>472300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>486800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>499900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>486600</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>36479500</v>
+      </c>
+      <c r="E48" s="3">
         <v>35038600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>37521600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>32913900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>32977900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>34013900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>32624400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>32770100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>34709800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>35155800</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>209100</v>
+      </c>
+      <c r="E49" s="3">
         <v>213000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>254300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>249400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>251000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>276900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>301200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>136300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>136900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>135500</v>
       </c>
     </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1937,8 +2051,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1969,40 +2086,46 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1111500</v>
+      </c>
+      <c r="E52" s="3">
         <v>966600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1089100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>961200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>937200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>937800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>866200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>871200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>855500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>861400</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2033,40 +2156,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>46751100</v>
+      </c>
+      <c r="E54" s="3">
         <v>45860500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>48904400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>42980600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>43386200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>44630800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>43020000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>42984600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>46059800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>47014200</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2079,8 +2208,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2093,200 +2223,219 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>101700</v>
+      </c>
+      <c r="E57" s="3">
         <v>2207200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>105900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>100800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>90500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2063900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>92100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>122300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1947800</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1972800</v>
+      </c>
+      <c r="E58" s="3">
         <v>2105800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1534900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1308100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1799900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2248300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2152100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2279600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3344300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3744900</v>
       </c>
     </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4977000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2552900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5750100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4940100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5150300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2236400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4294000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3922500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4139600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2212800</v>
       </c>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7197000</v>
+      </c>
+      <c r="E60" s="3">
         <v>7596900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7540300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6479500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7171100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7158300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6664400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6451300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7621700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8583900</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18289400</v>
+      </c>
+      <c r="E61" s="3">
         <v>17155100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>19079200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>17263600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>17368600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>17946000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>17559600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>17640800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>18646700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>18438400</v>
       </c>
     </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>376700</v>
+      </c>
+      <c r="E62" s="3">
         <v>349900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>360200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>304900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>301100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>294000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>256000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>244400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>255600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>263500</v>
       </c>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2317,8 +2466,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2349,8 +2501,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2381,40 +2536,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>32773700</v>
+      </c>
+      <c r="E66" s="3">
         <v>31866900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>33978200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>29932900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>30661400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>31315700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>30179700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>29996900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>32425200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>33095000</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2427,8 +2588,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2459,8 +2621,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2491,8 +2656,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2523,8 +2691,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2555,40 +2726,46 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>12214600</v>
+      </c>
+      <c r="E72" s="3">
         <v>12218800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>13021100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>11351200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>11029700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>11555100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11166400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>11272400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>11841200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>12049300</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2619,8 +2796,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2651,8 +2831,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2683,40 +2866,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13484900</v>
+      </c>
+      <c r="E76" s="3">
         <v>13501900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>14383000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12575500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12266500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12823100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12347400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12493500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13101700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13360100</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2747,45 +2936,51 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2816,8 +3011,11 @@
       <c r="L81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2830,40 +3028,44 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" s="3">
         <v>2455700</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F83" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3">
         <v>2603300</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M83" s="3">
         <v>2566100</v>
       </c>
     </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2894,8 +3096,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2926,8 +3131,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2958,8 +3166,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2990,8 +3201,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3022,40 +3236,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1346200</v>
+      </c>
+      <c r="E89" s="3">
         <v>1835700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>862500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1259200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>989500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2165800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1267200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2553600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1005700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1223200</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3068,40 +3288,44 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-679100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1088400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-479200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-475400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-444400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-945000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-516000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-374300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-474400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-712400</v>
       </c>
     </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3132,8 +3356,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3164,40 +3391,46 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-639600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1199000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-464500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-379500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-480700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-819600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-505300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-219100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>310300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-653400</v>
       </c>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3210,40 +3443,44 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3">
         <v>325000</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>343500</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3">
         <v>227100</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>320500</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M96" s="3">
         <v>262700</v>
       </c>
     </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3274,8 +3511,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3306,8 +3546,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3338,100 +3581,112 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-361100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-445100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-464500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1236600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-710900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-734000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-325200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1566100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-251000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-239300</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>300</v>
+      </c>
+      <c r="E101" s="3">
         <v>6800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-9600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>7200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>349300</v>
+      </c>
+      <c r="E102" s="3">
         <v>220200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-89400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-355000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-201800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>619000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>427100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>775500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1065600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>330200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TNABY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TNABY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="92">
   <si>
     <t>TNABY</t>
   </si>
@@ -656,73 +656,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -759,8 +763,11 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -797,8 +804,11 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -835,8 +845,11 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -851,8 +864,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -889,8 +903,11 @@
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,8 +944,11 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -965,8 +985,11 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1003,8 +1026,11 @@
       <c r="N15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1016,8 +1042,9 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1054,8 +1081,11 @@
       <c r="N17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1092,8 +1122,11 @@
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1108,8 +1141,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1146,8 +1180,11 @@
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1184,8 +1221,11 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1222,8 +1262,11 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1260,8 +1303,11 @@
       <c r="N23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1298,8 +1344,11 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1336,8 +1385,11 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1374,8 +1426,11 @@
       <c r="N26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1412,8 +1467,11 @@
       <c r="N27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1450,8 +1508,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1488,8 +1549,11 @@
       <c r="N29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1526,8 +1590,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1564,8 +1631,11 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1602,8 +1672,11 @@
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1640,8 +1713,11 @@
       <c r="N33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1678,8 +1754,11 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1716,51 +1795,57 @@
       <c r="N35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1775,8 +1860,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1791,350 +1877,378 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2381000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3911700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3779000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3402300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3451400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3094300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3444500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3754800</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M41" s="3">
         <v>2652600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1984200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>926100</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>911500</v>
+      </c>
+      <c r="E42" s="3">
         <v>813100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>916700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1015800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>782300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>648800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>717400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>748600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3960700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>979900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1264300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2156000</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3180300</v>
+      </c>
+      <c r="E43" s="3">
         <v>3217000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3018800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3737500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4493900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3894300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3798400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3510000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4190700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4463900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5887400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6269000</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>576000</v>
+      </c>
+      <c r="E44" s="3">
         <v>549000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>509400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>568900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>528000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>502400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>557600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>601200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>492800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>409900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>518000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>751300</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>236700</v>
+      </c>
+      <c r="E45" s="3">
         <v>169500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>184900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>245900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>168800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>147600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>142500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>195600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>48800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>89200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>72800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>121800</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7331600</v>
+      </c>
+      <c r="E46" s="3">
         <v>8708000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8454200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9014900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9480800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8336700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8709400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8860600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8692900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8645800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9779800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10286800</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>382100</v>
+      </c>
+      <c r="E47" s="3">
         <v>443200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>418300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>429300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>461400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>437600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>434200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>456400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>472300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>486800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>499900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>486600</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>38787000</v>
+      </c>
+      <c r="E48" s="3">
         <v>38617000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>36479500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>35038600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>37521600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>32913900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>32977900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>34013900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>32624400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>32770100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>34709800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>35155800</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>222600</v>
+      </c>
+      <c r="E49" s="3">
         <v>226000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>209100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>213000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>254300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>249400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>251000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>276900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>301200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>136300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>136900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>135500</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2171,8 +2285,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2209,46 +2326,52 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>438500</v>
+      </c>
+      <c r="E52" s="3">
         <v>1160400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1111500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>966600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1089100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>961200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>937200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>937800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>866200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>871200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>855500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>861400</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2285,46 +2408,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>47243300</v>
+      </c>
+      <c r="E54" s="3">
         <v>49243600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>46751100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>45860500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>48904400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>42980600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>43386200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>44630800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>43020000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>42984600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>46059800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>47014200</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2339,8 +2468,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2355,236 +2485,255 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>83800</v>
+      </c>
+      <c r="E57" s="3">
         <v>97700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>101700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2207200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>105900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>100800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>90500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2063900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>92100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>122300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1947800</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2065200</v>
+      </c>
+      <c r="E58" s="3">
         <v>1994300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1972800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2105800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1534900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1308100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1799900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2248300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2152100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2279600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3344300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3744900</v>
       </c>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5951100</v>
+      </c>
+      <c r="E59" s="3">
         <v>5190300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4977000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2552900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5750100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4940100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5150300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2236400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4294000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3922500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4139600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2212800</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8253500</v>
+      </c>
+      <c r="E60" s="3">
         <v>7435500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7197000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7596900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7540300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6479500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7171100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7158300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6664400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6451300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7621700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8583900</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18901800</v>
+      </c>
+      <c r="E61" s="3">
         <v>19140600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18289400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>17155100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>19079200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>17263600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>17368600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>17946000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>17559600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>17640800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>18646700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>18438400</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>451000</v>
+      </c>
+      <c r="E62" s="3">
         <v>424700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>376700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>349900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>360200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>304900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>301100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>294000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>256000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>244400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>255600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>263500</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2621,8 +2770,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2659,8 +2811,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2697,46 +2852,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>34976700</v>
+      </c>
+      <c r="E66" s="3">
         <v>34278200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>32773700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>31866900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>33978200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>29932900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>30661400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>31315700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>30179700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>29996900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>32425200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>33095000</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2751,8 +2912,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2789,8 +2951,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2827,8 +2992,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2865,8 +3033,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2903,46 +3074,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10498600</v>
+      </c>
+      <c r="E72" s="3">
         <v>13136200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>12214600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>12218800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>13021100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>11351200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11029700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>11555100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>11166400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>11272400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>11841200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>12049300</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2979,8 +3156,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3017,8 +3197,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3055,46 +3238,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11738500</v>
+      </c>
+      <c r="E76" s="3">
         <v>14442700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13484900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13501900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14383000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12575500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12266500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12823100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12347400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12493500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13101700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13360100</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3131,51 +3320,57 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3212,8 +3407,11 @@
       <c r="N81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3228,8 +3426,9 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3239,35 +3438,38 @@
       <c r="E83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G83" s="3">
         <v>2455700</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H83" s="3" t="s">
         <v>4</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K83" s="3">
         <v>2603300</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O83" s="3">
         <v>2566100</v>
       </c>
     </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3304,8 +3506,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3342,8 +3547,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3380,8 +3588,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3418,8 +3629,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3456,46 +3670,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>64200</v>
+      </c>
+      <c r="E89" s="3">
         <v>1360400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1346200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1835700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>862500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1259200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>989500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2165800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1267200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2553600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1005700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1223200</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3510,46 +3730,50 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1090900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-847700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-679100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1088400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-479200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-475400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-444400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-945000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-516000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-374300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-474400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-712400</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3586,8 +3810,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3624,46 +3851,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1140700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-651800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-639600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1199000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-464500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-379500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-480700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-819600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-505300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-219100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>310300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-653400</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3678,46 +3911,50 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>358800</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3">
         <v>325000</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>343500</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K96" s="3">
         <v>227100</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>320500</v>
       </c>
-      <c r="M96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="3">
         <v>262700</v>
       </c>
     </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3754,8 +3991,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3792,8 +4032,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3830,118 +4073,130 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-452900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-751000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-361100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-445100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-464500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1236600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-710900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-734000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-325200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1566100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-251000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-239300</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-22900</v>
+      </c>
+      <c r="E101" s="3">
         <v>1900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>6800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-9600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>7200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1533200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-67600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>349300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>220200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-89400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-355000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-201800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>619000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>427100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>775500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1065600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>330200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TNABY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TNABY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="92">
   <si>
     <t>TNABY</t>
   </si>
@@ -656,77 +656,84 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -766,8 +773,14 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -807,8 +820,14 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -848,8 +867,14 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -865,8 +890,10 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -906,8 +933,14 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -947,8 +980,14 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -988,8 +1027,14 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1029,8 +1074,14 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1043,8 +1094,10 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1084,8 +1137,14 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1125,8 +1184,14 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1142,8 +1207,10 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1183,8 +1250,14 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1224,8 +1297,14 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1265,8 +1344,14 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1306,8 +1391,14 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1347,8 +1438,14 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1388,8 +1485,14 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1429,8 +1532,14 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1470,8 +1579,14 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1511,8 +1626,14 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1552,8 +1673,14 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1593,8 +1720,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1634,8 +1767,14 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1675,8 +1814,14 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1716,8 +1861,14 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1757,8 +1908,14 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1798,54 +1955,66 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1861,8 +2030,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1878,377 +2049,433 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3271100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2623800</v>
+      </c>
+      <c r="F41" s="3">
         <v>2381000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>3911700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>3779000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>3402300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>3451400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>3094300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>3444500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3754800</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O41" s="3">
         <v>2652600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1984200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>926100</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>453500</v>
+      </c>
+      <c r="E42" s="3">
+        <v>502100</v>
+      </c>
+      <c r="F42" s="3">
         <v>911500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>813100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>916700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>1015800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>782300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>648800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>717400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>748600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>3960700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>979900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>1264300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>2156000</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3177200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2798100</v>
+      </c>
+      <c r="F43" s="3">
         <v>3180300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>3217000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>3018800</v>
       </c>
-      <c r="G43" s="3">
-        <v>3737500</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
+        <v>3479600</v>
+      </c>
+      <c r="J43" s="3">
         <v>4493900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>3894300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>3798400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>3510000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>4190700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>4463900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>5887400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>6269000</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>575600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>631000</v>
+      </c>
+      <c r="F44" s="3">
         <v>576000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>549000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>509400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>568900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>528000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>502400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>557600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>601200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>492800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>409900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>518000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>751300</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>305500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>423600</v>
+      </c>
+      <c r="F45" s="3">
         <v>236700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>169500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>184900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>245900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>168800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>147600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>142500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>195600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>48800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>89200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>72800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>121800</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7828500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>7023900</v>
+      </c>
+      <c r="F46" s="3">
         <v>7331600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>8708000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>8454200</v>
       </c>
-      <c r="G46" s="3">
-        <v>9014900</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
+        <v>8756900</v>
+      </c>
+      <c r="J46" s="3">
         <v>9480800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>8336700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>8709400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>8860600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>8692900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>8645800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>9779800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>10286800</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>384100</v>
+      </c>
+      <c r="E47" s="3">
+        <v>419700</v>
+      </c>
+      <c r="F47" s="3">
         <v>382100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>443200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>418300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>429300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>461400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>437600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>434200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>456400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>472300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>486800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>499900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>486600</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>41220700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>40757500</v>
+      </c>
+      <c r="F48" s="3">
         <v>38787000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>38617000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>36479500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>35038600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>37521600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>32913900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>32977900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>34013900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>32624400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>32770100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>34709800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>35155800</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>178100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>180300</v>
+      </c>
+      <c r="F49" s="3">
         <v>222600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>226000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>209100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>213000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>254300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>249400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>251000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>276900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>301200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>136300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>136900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>135500</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2288,8 +2515,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2329,49 +2562,61 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>377000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>239600</v>
+      </c>
+      <c r="F52" s="3">
         <v>438500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>1160400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>1111500</v>
       </c>
-      <c r="G52" s="3">
-        <v>966600</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
+        <v>178800</v>
+      </c>
+      <c r="J52" s="3">
         <v>1089100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>961200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>937200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>937800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>866200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>871200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>855500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>861400</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2411,49 +2656,61 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>50091000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>48857000</v>
+      </c>
+      <c r="F54" s="3">
         <v>47243300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>49243600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>46751100</v>
       </c>
-      <c r="G54" s="3">
-        <v>45860500</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
+        <v>44814800</v>
+      </c>
+      <c r="J54" s="3">
         <v>48904400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>42980600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>43386200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>44630800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>43020000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>42984600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>46059800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>47014200</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2469,8 +2726,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2486,254 +2745,292 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>92900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1776000</v>
+      </c>
+      <c r="F57" s="3">
         <v>83800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>97700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>101700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2207200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>105900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>100800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>90500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2063900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>92100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>122300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>3600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1947800</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3711800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3578900</v>
+      </c>
+      <c r="F58" s="3">
         <v>2065200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1994300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1972800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>2105800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1534900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1308100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1799900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2248300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>2152100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>2279600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>3344300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>3744900</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5699500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2981100</v>
+      </c>
+      <c r="F59" s="3">
         <v>5951100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>5190300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>4977000</v>
       </c>
-      <c r="G59" s="3">
-        <v>2552900</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
+        <v>3858400</v>
+      </c>
+      <c r="J59" s="3">
         <v>5750100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>4940100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>5150300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2236400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>4294000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>3922500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>4139600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>2212800</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9687800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>9012000</v>
+      </c>
+      <c r="F60" s="3">
         <v>8253500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>7435500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>7197000</v>
       </c>
-      <c r="G60" s="3">
-        <v>7596900</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
+        <v>8902500</v>
+      </c>
+      <c r="J60" s="3">
         <v>7540300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>6479500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>7171100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>7158300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>6664400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>6451300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>7621700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>8583900</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>19021300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>18483900</v>
+      </c>
+      <c r="F61" s="3">
         <v>18901800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>19140600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>18289400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>17155100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>19079200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>17263600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>17368600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>17946000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>17559600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>17640800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>18646700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>18438400</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>488300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>462000</v>
+      </c>
+      <c r="F62" s="3">
         <v>451000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>424700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>376700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>349900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>360200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>304900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>301100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>294000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>256000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>244400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>255600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>263500</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2773,8 +3070,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2814,8 +3117,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2855,49 +3164,61 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>37123300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>35808900</v>
+      </c>
+      <c r="F66" s="3">
         <v>34976700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>34278200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>32773700</v>
       </c>
-      <c r="G66" s="3">
-        <v>31866900</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
+        <v>33182500</v>
+      </c>
+      <c r="J66" s="3">
         <v>33978200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>29932900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>30661400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>31315700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>30179700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>29996900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>32425200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>33095000</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2913,8 +3234,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2954,8 +3277,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2995,8 +3324,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3036,8 +3371,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3077,49 +3418,61 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>11197000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>11298600</v>
+      </c>
+      <c r="F72" s="3">
         <v>10498600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>13136200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>12214600</v>
       </c>
-      <c r="G72" s="3">
-        <v>12218800</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
+        <v>9857400</v>
+      </c>
+      <c r="J72" s="3">
         <v>13021100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>11351200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>11029700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>11555100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>11166400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>11272400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>11841200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>12049300</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3159,8 +3512,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3200,8 +3559,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3241,49 +3606,61 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12431800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>12510000</v>
+      </c>
+      <c r="F76" s="3">
         <v>11738500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>14442700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>13484900</v>
       </c>
-      <c r="G76" s="3">
-        <v>13501900</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
+        <v>11140500</v>
+      </c>
+      <c r="J76" s="3">
         <v>14383000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>12575500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>12266500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>12823100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>12347400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>12493500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>13101700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>13360100</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3323,54 +3700,66 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3410,8 +3799,14 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3427,49 +3822,57 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>4</v>
+      <c r="D83" s="3">
+        <v>646000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>2512100</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3">
         <v>2455700</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M83" s="3">
         <v>2603300</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q83" s="3">
         <v>2566100</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3509,8 +3912,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3550,8 +3959,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3591,8 +4006,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3632,8 +4053,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3673,49 +4100,61 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1396000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>950700</v>
+      </c>
+      <c r="F89" s="3">
         <v>64200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1360400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>1346200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>1835700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>862500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1259200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>989500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>2165800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1267200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>2553600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1005700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>1223200</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3731,49 +4170,57 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-751500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-1255300</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1090900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-847700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-679100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-1088400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-479200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-475400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-444400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-945000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-516000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-374300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-474400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-712400</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3813,8 +4260,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3854,49 +4307,61 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-777900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-681900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1140700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-651800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-639600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1199000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-464500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-379500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-480700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-819600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-505300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-219100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>310300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-653400</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3912,49 +4377,57 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E96" s="3">
+        <v>358900</v>
+      </c>
+      <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>358800</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3">
         <v>325000</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>343500</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M96" s="3">
         <v>227100</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>320500</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q96" s="3">
         <v>262700</v>
       </c>
     </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3994,8 +4467,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4035,8 +4514,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4076,127 +4561,151 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-124100</v>
+      </c>
+      <c r="F100" s="3">
         <v>-452900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-751000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-361100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-445100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-464500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-1236600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-710900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-734000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-325200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-1566100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-251000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-239300</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E101" s="3">
+        <v>28500</v>
+      </c>
+      <c r="F101" s="3">
         <v>-22900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>1900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>6800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-9600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>7200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-2700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>2800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>640200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>155000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1533200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-67600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>349300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>220200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-89400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-355000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-201800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>619000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>427100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>775500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>1065600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>330200</v>
       </c>
     </row>
